--- a/seed_data/starrings_new.xlsx
+++ b/seed_data/starrings_new.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/seed_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{387DE9DB-07CF-4049-826E-5FAF1F9EE2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="14_{387DE9DB-07CF-4049-826E-5FAF1F9EE2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF81E560-4F18-46F8-8DEC-CFA955332B44}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>May2026</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>Player</t>
+  </si>
+  <si>
+    <t>July2026</t>
   </si>
 </sst>
 </file>
@@ -542,10 +545,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>59</v>
       </c>
@@ -555,8 +558,11 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -566,16 +572,22 @@
       <c r="C2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -583,7 +595,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -593,8 +605,11 @@
       <c r="C5">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -604,8 +619,11 @@
       <c r="C6">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -615,8 +633,11 @@
       <c r="C7">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -626,8 +647,11 @@
       <c r="C8">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -637,8 +661,11 @@
       <c r="C9">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -648,8 +675,11 @@
       <c r="C10">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -659,8 +689,11 @@
       <c r="C11">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -670,8 +703,11 @@
       <c r="C12">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -681,8 +717,11 @@
       <c r="C13">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -692,8 +731,11 @@
       <c r="C14">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -703,8 +745,11 @@
       <c r="C15">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -714,8 +759,11 @@
       <c r="C16">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -725,8 +773,11 @@
       <c r="C17">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -736,8 +787,11 @@
       <c r="C18">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -747,8 +801,11 @@
       <c r="C19">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -758,8 +815,11 @@
       <c r="C20">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -769,8 +829,11 @@
       <c r="C21">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -780,8 +843,11 @@
       <c r="C22">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -789,7 +855,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -799,8 +865,11 @@
       <c r="C24">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -810,8 +879,11 @@
       <c r="C25">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -821,8 +893,11 @@
       <c r="C26">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -832,8 +907,11 @@
       <c r="C27">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -841,7 +919,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -851,8 +929,11 @@
       <c r="C29">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -860,7 +941,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -870,8 +951,11 @@
       <c r="C31">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -881,8 +965,11 @@
       <c r="C32">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -892,8 +979,11 @@
       <c r="C33">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -904,7 +994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -914,8 +1004,11 @@
       <c r="C35">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -925,8 +1018,11 @@
       <c r="C36">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -936,8 +1032,11 @@
       <c r="C37">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -947,8 +1046,11 @@
       <c r="C38">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -958,8 +1060,11 @@
       <c r="C39">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -969,8 +1074,11 @@
       <c r="C40">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -980,8 +1088,11 @@
       <c r="C41">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -991,8 +1102,11 @@
       <c r="C42">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -1002,8 +1116,11 @@
       <c r="C43">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1013,8 +1130,11 @@
       <c r="C44">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -1024,8 +1144,11 @@
       <c r="C45">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -1036,7 +1159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -1047,7 +1170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1058,7 +1181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -1066,75 +1189,102 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C50">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C51">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C52">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C53">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C54">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C55">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C56">
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C57">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
       <c r="C58">
+        <v>3.2</v>
+      </c>
+      <c r="D58">
         <v>3.2</v>
       </c>
     </row>
